--- a/outputs/templates/假设开发法测算_模板.xlsx
+++ b/outputs/templates/假设开发法测算_模板.xlsx
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D11" s="10">
-        <f>B10+C10</f>
+        <f>ROUND(B10+C10,0)</f>
         <v/>
       </c>
     </row>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="D15" s="12">
-        <f>B15*B7</f>
+        <f>ROUND(B15*B7,0)</f>
         <v/>
       </c>
     </row>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B21" s="12">
-        <f>B17*管理费率</f>
+        <f>ROUND(B17*管理费率,0)</f>
         <v/>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B22" s="12">
-        <f>D14*销售费率</f>
+        <f>ROUND(D14*销售费率,0)</f>
         <v/>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="B23" s="12">
-        <f>D15*税率</f>
+        <f>ROUND(D15*税率,0)</f>
         <v/>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B25" s="12">
-        <f>SUM(B20:B24)</f>
+        <f>ROUND(SUM(B20:B24),0)</f>
         <v/>
       </c>
     </row>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B32" s="12">
-        <f>D16/(1+B28)^((C11+C10)/12)</f>
+        <f>ROUND(D16/(1+B28)^((C11+C10)/12),0)</f>
         <v/>
       </c>
       <c r="C32" s="19" t="inlineStr">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="B33" s="12">
-        <f>B20/(1+B28)^(D20/12)</f>
+        <f>ROUND(B20/(1+B28)^(D20/12),0)</f>
         <v/>
       </c>
       <c r="C33" s="19" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B34" s="12">
-        <f>B21/(1+B28)^(D21/12)</f>
+        <f>ROUND(B21/(1+B28)^(D21/12),0)</f>
         <v/>
       </c>
       <c r="C34" s="19" t="inlineStr"/>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="B35" s="12">
-        <f>B22/(1+B28)^(D22/12)</f>
+        <f>ROUND(B22/(1+B28)^(D22/12),0)</f>
         <v/>
       </c>
       <c r="C35" s="19" t="inlineStr"/>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B36" s="12">
-        <f>B23/(1+B28)^(D23/12)</f>
+        <f>ROUND(B23/(1+B28)^(D23/12),0)</f>
         <v/>
       </c>
       <c r="C36" s="19" t="inlineStr"/>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="B37" s="12">
-        <f>B24/(1+B28)^(D24/12)</f>
+        <f>ROUND(B24/(1+B28)^(D24/12),0)</f>
         <v/>
       </c>
       <c r="C37" s="19" t="inlineStr">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B38" s="12">
-        <f>SUM(B33:B37)</f>
+        <f>ROUND(SUM(B33:B37),0)</f>
         <v/>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B39" s="21">
-        <f>B32-B38</f>
+        <f>ROUND(B32-B38,0)</f>
         <v/>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B41" s="21">
-        <f>B39/B40</f>
+        <f>ROUND(B39/B40,0)</f>
         <v/>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="12">
-        <f>B4-C4</f>
+        <f>ROUND(B4-C4,0)</f>
         <v/>
       </c>
       <c r="E4" s="25">
@@ -1201,7 +1201,7 @@
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="8" t="n"/>
       <c r="D5" s="12">
-        <f>B5-C5</f>
+        <f>ROUND(B5-C5,0)</f>
         <v/>
       </c>
       <c r="E5" s="25">
@@ -1216,7 +1216,7 @@
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="12">
-        <f>B6-C6</f>
+        <f>ROUND(B6-C6,0)</f>
         <v/>
       </c>
       <c r="E6" s="25">
@@ -1231,7 +1231,7 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="12">
-        <f>B7-C7</f>
+        <f>ROUND(B7-C7,0)</f>
         <v/>
       </c>
       <c r="E7" s="25">
@@ -1246,7 +1246,7 @@
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="12">
-        <f>B8-C8</f>
+        <f>ROUND(B8-C8,0)</f>
         <v/>
       </c>
       <c r="E8" s="25">
@@ -1261,7 +1261,7 @@
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="12">
-        <f>B9-C9</f>
+        <f>ROUND(B9-C9,0)</f>
         <v/>
       </c>
       <c r="E9" s="25">
@@ -1276,7 +1276,7 @@
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="12">
-        <f>B10-C10</f>
+        <f>ROUND(B10-C10,0)</f>
         <v/>
       </c>
       <c r="E10" s="25">
@@ -1291,7 +1291,7 @@
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="12">
-        <f>B11-C11</f>
+        <f>ROUND(B11-C11,0)</f>
         <v/>
       </c>
       <c r="E11" s="25">
@@ -1306,7 +1306,7 @@
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="12">
-        <f>B12-C12</f>
+        <f>ROUND(B12-C12,0)</f>
         <v/>
       </c>
       <c r="E12" s="25">
@@ -1321,7 +1321,7 @@
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="12">
-        <f>B13-C13</f>
+        <f>ROUND(B13-C13,0)</f>
         <v/>
       </c>
       <c r="E13" s="25">
@@ -1336,7 +1336,7 @@
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="12">
-        <f>B14-C14</f>
+        <f>ROUND(B14-C14,0)</f>
         <v/>
       </c>
       <c r="E14" s="25">
@@ -1351,7 +1351,7 @@
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="12">
-        <f>B15-C15</f>
+        <f>ROUND(B15-C15,0)</f>
         <v/>
       </c>
       <c r="E15" s="25">
@@ -1366,7 +1366,7 @@
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="12">
-        <f>B16-C16</f>
+        <f>ROUND(B16-C16,0)</f>
         <v/>
       </c>
       <c r="E16" s="25">
@@ -1381,7 +1381,7 @@
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="12">
-        <f>B17-C17</f>
+        <f>ROUND(B17-C17,0)</f>
         <v/>
       </c>
       <c r="E17" s="25">
@@ -1396,7 +1396,7 @@
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="12">
-        <f>B18-C18</f>
+        <f>ROUND(B18-C18,0)</f>
         <v/>
       </c>
       <c r="E18" s="25">
@@ -1411,7 +1411,7 @@
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="12">
-        <f>B19-C19</f>
+        <f>ROUND(B19-C19,0)</f>
         <v/>
       </c>
       <c r="E19" s="25">
@@ -1426,7 +1426,7 @@
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="12">
-        <f>B20-C20</f>
+        <f>ROUND(B20-C20,0)</f>
         <v/>
       </c>
       <c r="E20" s="25">
@@ -1441,7 +1441,7 @@
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="12">
-        <f>B21-C21</f>
+        <f>ROUND(B21-C21,0)</f>
         <v/>
       </c>
       <c r="E21" s="25">
@@ -1456,7 +1456,7 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="12">
-        <f>B22-C22</f>
+        <f>ROUND(B22-C22,0)</f>
         <v/>
       </c>
       <c r="E22" s="25">
@@ -1471,7 +1471,7 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="12">
-        <f>B23-C23</f>
+        <f>ROUND(B23-C23,0)</f>
         <v/>
       </c>
       <c r="E23" s="25">
@@ -1486,7 +1486,7 @@
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="12">
-        <f>B24-C24</f>
+        <f>ROUND(B24-C24,0)</f>
         <v/>
       </c>
       <c r="E24" s="25">
@@ -1501,7 +1501,7 @@
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="12">
-        <f>B25-C25</f>
+        <f>ROUND(B25-C25,0)</f>
         <v/>
       </c>
       <c r="E25" s="25">
@@ -1516,7 +1516,7 @@
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="12">
-        <f>B26-C26</f>
+        <f>ROUND(B26-C26,0)</f>
         <v/>
       </c>
       <c r="E26" s="25">
@@ -1531,7 +1531,7 @@
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="12">
-        <f>B27-C27</f>
+        <f>ROUND(B27-C27,0)</f>
         <v/>
       </c>
       <c r="E27" s="25">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="D28" s="21">
-        <f>SUMPRODUCT(D4:D27,E4:E27)</f>
+        <f>ROUND(SUMPRODUCT(D4:D27,E4:E27),0)</f>
         <v/>
       </c>
     </row>

--- a/outputs/templates/假设开发法测算_模板.xlsx
+++ b/outputs/templates/假设开发法测算_模板.xlsx
@@ -726,7 +726,9 @@
           <t>单价 (元/m²)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>25000</v>
+      </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>总价 (元)</t>

--- a/outputs/templates/假设开发法测算_模板.xlsx
+++ b/outputs/templates/假设开发法测算_模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="假设开发法" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现金流时间线" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="假设开发法" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="现金流时间线" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/templates/假设开发法测算_模板.xlsx
+++ b/outputs/templates/假设开发法测算_模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="假设开发法" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="现金流时间线" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="假设开发法" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现金流时间线" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
